--- a/public/westpoint/misc-lessons/assets/MA153X_Linear_Regression_Boardsheet.xlsx
+++ b/public/westpoint/misc-lessons/assets/MA153X_Linear_Regression_Boardsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/dusty_turner_westpoint_edu/Documents/Teaching/courses/misc-lessons/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="11_99D81327CEA3E08162DF7967D7DAE942CFE87385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E9DDB2F-A6B4-4D76-A268-4804E82BEFD0}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="11_99D81327CEA3E08162DF7967D7DAE942CFE87385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{881659E1-BBCC-4573-A645-183616A87833}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -124,231 +124,276 @@
     <t>Hint: Intercept Formula</t>
   </si>
   <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>=SLOPE(C2:C38,B2:B38)</t>
+  </si>
+  <si>
+    <t>=INTERCEPT(C2:C38,B2:B38)</t>
+  </si>
+  <si>
     <t>S002</t>
   </si>
   <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>S007</t>
+  </si>
+  <si>
+    <t>S008</t>
+  </si>
+  <si>
+    <t>S009</t>
+  </si>
+  <si>
+    <t>S010</t>
+  </si>
+  <si>
+    <t>S011</t>
+  </si>
+  <si>
+    <t>S012</t>
+  </si>
+  <si>
+    <t>S013</t>
+  </si>
+  <si>
+    <t>S014</t>
+  </si>
+  <si>
+    <t>S015</t>
+  </si>
+  <si>
+    <t>S016</t>
+  </si>
+  <si>
+    <t>S017</t>
+  </si>
+  <si>
+    <t>S018</t>
+  </si>
+  <si>
+    <t>S019</t>
+  </si>
+  <si>
+    <t>S020</t>
+  </si>
+  <si>
+    <t>S021</t>
+  </si>
+  <si>
+    <t>S022</t>
+  </si>
+  <si>
+    <t>S023</t>
+  </si>
+  <si>
+    <t>S024</t>
+  </si>
+  <si>
+    <t>S025</t>
+  </si>
+  <si>
+    <t>S026</t>
+  </si>
+  <si>
+    <t>S027</t>
+  </si>
+  <si>
+    <t>S028</t>
+  </si>
+  <si>
+    <t>S029</t>
+  </si>
+  <si>
+    <t>S030</t>
+  </si>
+  <si>
+    <t>S031</t>
+  </si>
+  <si>
+    <t>S032</t>
+  </si>
+  <si>
+    <t>S033</t>
+  </si>
+  <si>
+    <t>S034</t>
+  </si>
+  <si>
+    <t>S035</t>
+  </si>
+  <si>
+    <t>S036</t>
+  </si>
+  <si>
+    <t>S037</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Predicted (lbs)</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>|Error|</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Actual Weight (lbs)</t>
+  </si>
+  <si>
+    <t>Fitted (lbs)</t>
+  </si>
+  <si>
+    <t>Residual (lbs)</t>
+  </si>
+  <si>
     <t>74</t>
   </si>
   <si>
     <t>239</t>
   </si>
   <si>
-    <t>=SLOPE(C2:C38,B2:B38)</t>
-  </si>
-  <si>
-    <t>=INTERCEPT(C2:C38,B2:B38)</t>
-  </si>
-  <si>
-    <t>S003</t>
-  </si>
-  <si>
     <t>63</t>
   </si>
   <si>
     <t>147</t>
   </si>
   <si>
-    <t>S004</t>
-  </si>
-  <si>
     <t>70</t>
   </si>
   <si>
     <t>169</t>
   </si>
   <si>
-    <t>S005</t>
-  </si>
-  <si>
     <t>68</t>
   </si>
   <si>
     <t>159</t>
   </si>
   <si>
-    <t>S006</t>
-  </si>
-  <si>
     <t>72</t>
   </si>
   <si>
     <t>211</t>
   </si>
   <si>
-    <t>S007</t>
-  </si>
-  <si>
     <t>73</t>
   </si>
   <si>
-    <t>S008</t>
-  </si>
-  <si>
     <t>71</t>
   </si>
   <si>
     <t>202</t>
   </si>
   <si>
-    <t>S009</t>
-  </si>
-  <si>
     <t>64</t>
   </si>
   <si>
     <t>136</t>
   </si>
   <si>
-    <t>S010</t>
-  </si>
-  <si>
     <t>67</t>
   </si>
   <si>
     <t>194</t>
   </si>
   <si>
-    <t>S011</t>
-  </si>
-  <si>
     <t>208</t>
   </si>
   <si>
-    <t>S012</t>
-  </si>
-  <si>
     <t>196</t>
   </si>
   <si>
-    <t>S013</t>
-  </si>
-  <si>
     <t>66</t>
   </si>
   <si>
     <t>209</t>
   </si>
   <si>
-    <t>S014</t>
-  </si>
-  <si>
     <t>69</t>
   </si>
   <si>
     <t>175</t>
   </si>
   <si>
-    <t>S015</t>
-  </si>
-  <si>
     <t>177</t>
   </si>
   <si>
-    <t>S017</t>
-  </si>
-  <si>
     <t>186</t>
   </si>
   <si>
-    <t>S019</t>
-  </si>
-  <si>
     <t>205</t>
   </si>
   <si>
-    <t>S020</t>
-  </si>
-  <si>
     <t>210</t>
   </si>
   <si>
-    <t>S021</t>
-  </si>
-  <si>
     <t>193</t>
   </si>
   <si>
-    <t>S022</t>
-  </si>
-  <si>
-    <t>S023</t>
-  </si>
-  <si>
     <t>138</t>
   </si>
   <si>
-    <t>S024</t>
-  </si>
-  <si>
     <t>163</t>
   </si>
   <si>
-    <t>S025</t>
-  </si>
-  <si>
     <t>185</t>
   </si>
   <si>
-    <t>S026</t>
-  </si>
-  <si>
     <t>65</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>S027</t>
-  </si>
-  <si>
     <t>149</t>
   </si>
   <si>
-    <t>S028</t>
-  </si>
-  <si>
     <t>62</t>
   </si>
   <si>
     <t>143</t>
   </si>
   <si>
-    <t>S029</t>
-  </si>
-  <si>
     <t>129</t>
   </si>
   <si>
-    <t>S030</t>
-  </si>
-  <si>
     <t>170</t>
   </si>
   <si>
-    <t>S032</t>
-  </si>
-  <si>
-    <t>S033</t>
-  </si>
-  <si>
     <t>206</t>
   </si>
   <si>
-    <t>S035</t>
-  </si>
-  <si>
     <t>61</t>
   </si>
   <si>
     <t>128</t>
   </si>
   <si>
-    <t>S036</t>
-  </si>
-  <si>
-    <t>S037</t>
-  </si>
-  <si>
     <t>235</t>
   </si>
   <si>
@@ -377,58 +422,13 @@
   </si>
   <si>
     <t>154</t>
-  </si>
-  <si>
-    <t>Actual Weight (lbs)</t>
-  </si>
-  <si>
-    <t>Predicted (lbs)</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
-  <si>
-    <t>|Error|</t>
-  </si>
-  <si>
-    <t>MAE</t>
-  </si>
-  <si>
-    <t>S001</t>
-  </si>
-  <si>
-    <t>S016</t>
-  </si>
-  <si>
-    <t>S018</t>
-  </si>
-  <si>
-    <t>S031</t>
-  </si>
-  <si>
-    <t>S034</t>
-  </si>
-  <si>
-    <t>Fitted (lbs)</t>
-  </si>
-  <si>
-    <t>Residual (lbs)</t>
-  </si>
-  <si>
-    <t>Set</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Train</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -463,10 +463,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,6 +484,599 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'L8 - Build Model'!$B$2:$B$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>66</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'L8 - Build Model'!$C$2:$C$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>154</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8819-4CAA-B6B3-2C293AAE94AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="213175304"/>
+        <c:axId val="208819208"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="213175304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="60"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="208819208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="208819208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="213175304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1081,6 +1673,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1636,7 +2268,564 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C31384CF-8C78-0456-9EE6-25C1BD3B6309}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1675,10 +2864,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1961,9 +3146,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1971,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1979,7 +3164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1987,7 +3172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1995,7 +3180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2003,7 +3188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2011,7 +3196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2019,7 +3204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2027,7 +3212,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2035,7 +3220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2043,7 +3228,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2060,16 +3245,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -2086,416 +3271,416 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2">
         <v>74</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>239</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B3">
+        <v>63</v>
+      </c>
+      <c r="C3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="B4">
+        <v>70</v>
+      </c>
+      <c r="C4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>72</v>
+      </c>
+      <c r="C6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7">
+        <v>73</v>
+      </c>
+      <c r="C7">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11">
+        <v>74</v>
+      </c>
+      <c r="C11">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12">
+        <v>67</v>
+      </c>
+      <c r="C12">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <v>66</v>
+      </c>
+      <c r="C13">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14">
+        <v>69</v>
+      </c>
+      <c r="C14">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15">
+        <v>68</v>
+      </c>
+      <c r="C15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16">
+        <v>67</v>
+      </c>
+      <c r="C16">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17">
+        <v>73</v>
+      </c>
+      <c r="C17">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <v>69</v>
+      </c>
+      <c r="C18">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19">
+        <v>72</v>
+      </c>
+      <c r="C19">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <v>74</v>
+      </c>
+      <c r="C20">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21">
+        <v>71</v>
+      </c>
+      <c r="C21">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22">
+        <v>64</v>
+      </c>
+      <c r="C22">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23">
+        <v>70</v>
+      </c>
+      <c r="C23">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25">
+        <v>70</v>
+      </c>
+      <c r="C25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <v>62</v>
+      </c>
+      <c r="C26">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27">
+        <v>66</v>
+      </c>
+      <c r="C27">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28">
+        <v>68</v>
+      </c>
+      <c r="C28">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29">
+        <v>71</v>
+      </c>
+      <c r="C29">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30">
+        <v>73</v>
+      </c>
+      <c r="C30">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31">
+        <v>61</v>
+      </c>
+      <c r="C31">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32">
+        <v>61</v>
+      </c>
+      <c r="C32">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>72</v>
+      </c>
+      <c r="C33">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>74</v>
+      </c>
+      <c r="C34">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35">
+        <v>68</v>
+      </c>
+      <c r="C35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="2">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="2">
-        <v>68</v>
-      </c>
-      <c r="C5" s="2">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="B36">
         <v>72</v>
       </c>
-      <c r="C6" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="2">
-        <v>73</v>
-      </c>
-      <c r="C7" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="2">
-        <v>71</v>
-      </c>
-      <c r="C8" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="C36">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2">
-        <v>67</v>
-      </c>
-      <c r="C10" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="2">
-        <v>74</v>
-      </c>
-      <c r="C11" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2">
-        <v>67</v>
-      </c>
-      <c r="C12" s="2">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="B37">
+        <v>72</v>
+      </c>
+      <c r="C37">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38">
         <v>66</v>
       </c>
-      <c r="C13" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="2">
-        <v>69</v>
-      </c>
-      <c r="C14" s="2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2">
-        <v>68</v>
-      </c>
-      <c r="C15" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="2">
-        <v>67</v>
-      </c>
-      <c r="C16" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="2">
-        <v>73</v>
-      </c>
-      <c r="C17" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="2">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="2">
-        <v>72</v>
-      </c>
-      <c r="C19" s="2">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="2">
-        <v>74</v>
-      </c>
-      <c r="C20" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="2">
-        <v>71</v>
-      </c>
-      <c r="C21" s="2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="2">
-        <v>64</v>
-      </c>
-      <c r="C22" s="2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="2">
-        <v>70</v>
-      </c>
-      <c r="C23" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="2">
-        <v>65</v>
-      </c>
-      <c r="C24" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="2">
-        <v>70</v>
-      </c>
-      <c r="C25" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="2">
-        <v>62</v>
-      </c>
-      <c r="C26" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="2">
-        <v>66</v>
-      </c>
-      <c r="C27" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="2">
-        <v>68</v>
-      </c>
-      <c r="C28" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="2">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="2">
-        <v>73</v>
-      </c>
-      <c r="C30" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="2">
-        <v>61</v>
-      </c>
-      <c r="C31" s="2">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" s="2">
-        <v>61</v>
-      </c>
-      <c r="C32" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="2">
-        <v>72</v>
-      </c>
-      <c r="C33" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="2">
-        <v>74</v>
-      </c>
-      <c r="C34" s="2">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="2">
-        <v>68</v>
-      </c>
-      <c r="C35" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="2">
-        <v>72</v>
-      </c>
-      <c r="C36" s="2">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="2">
-        <v>72</v>
-      </c>
-      <c r="C37" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" s="2">
-        <v>66</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="C38">
         <v>154</v>
       </c>
     </row>
@@ -2503,22 +3688,23 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F08A47-FA79-4CF1-8722-84C308B7709C}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -2535,14 +3721,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2">
         <v>74</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>239</v>
       </c>
       <c r="D2">
@@ -2554,399 +3740,399 @@
         <v>-233.24118728926112</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3">
         <v>63</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>70</v>
+      </c>
+      <c r="C4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="2">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B5">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>72</v>
+      </c>
+      <c r="C6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7">
+        <v>73</v>
+      </c>
+      <c r="C7">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11">
+        <v>74</v>
+      </c>
+      <c r="C11">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12">
+        <v>67</v>
+      </c>
+      <c r="C12">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <v>66</v>
+      </c>
+      <c r="C13">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14">
+        <v>69</v>
+      </c>
+      <c r="C14">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15">
         <v>68</v>
       </c>
-      <c r="C5" s="2">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="C15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16">
+        <v>67</v>
+      </c>
+      <c r="C16">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17">
+        <v>73</v>
+      </c>
+      <c r="C17">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <v>69</v>
+      </c>
+      <c r="C18">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19">
         <v>72</v>
       </c>
-      <c r="C6" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C19">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <v>74</v>
+      </c>
+      <c r="C20">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21">
+        <v>71</v>
+      </c>
+      <c r="C21">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22">
+        <v>64</v>
+      </c>
+      <c r="C22">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23">
+        <v>70</v>
+      </c>
+      <c r="C23">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25">
+        <v>70</v>
+      </c>
+      <c r="C25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <v>62</v>
+      </c>
+      <c r="C26">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27">
+        <v>66</v>
+      </c>
+      <c r="C27">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28">
+        <v>68</v>
+      </c>
+      <c r="C28">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29">
+        <v>71</v>
+      </c>
+      <c r="C29">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30">
         <v>73</v>
       </c>
-      <c r="C7" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="2">
-        <v>71</v>
-      </c>
-      <c r="C8" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="C30">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31">
+        <v>61</v>
+      </c>
+      <c r="C31">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32">
+        <v>61</v>
+      </c>
+      <c r="C32">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>72</v>
+      </c>
+      <c r="C33">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>74</v>
+      </c>
+      <c r="C34">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35">
+        <v>68</v>
+      </c>
+      <c r="C35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36">
+        <v>72</v>
+      </c>
+      <c r="C36">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2">
-        <v>67</v>
-      </c>
-      <c r="C10" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="2">
-        <v>74</v>
-      </c>
-      <c r="C11" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2">
-        <v>67</v>
-      </c>
-      <c r="C12" s="2">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="B37">
+        <v>72</v>
+      </c>
+      <c r="C37">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38">
         <v>66</v>
       </c>
-      <c r="C13" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="2">
-        <v>69</v>
-      </c>
-      <c r="C14" s="2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2">
-        <v>68</v>
-      </c>
-      <c r="C15" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="2">
-        <v>67</v>
-      </c>
-      <c r="C16" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="2">
-        <v>73</v>
-      </c>
-      <c r="C17" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="2">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="2">
-        <v>72</v>
-      </c>
-      <c r="C19" s="2">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="2">
-        <v>74</v>
-      </c>
-      <c r="C20" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="2">
-        <v>71</v>
-      </c>
-      <c r="C21" s="2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="2">
-        <v>64</v>
-      </c>
-      <c r="C22" s="2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="2">
-        <v>70</v>
-      </c>
-      <c r="C23" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="2">
-        <v>65</v>
-      </c>
-      <c r="C24" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="2">
-        <v>70</v>
-      </c>
-      <c r="C25" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="2">
-        <v>62</v>
-      </c>
-      <c r="C26" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="2">
-        <v>66</v>
-      </c>
-      <c r="C27" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="2">
-        <v>68</v>
-      </c>
-      <c r="C28" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="2">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="2">
-        <v>73</v>
-      </c>
-      <c r="C30" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="2">
-        <v>61</v>
-      </c>
-      <c r="C31" s="2">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" s="2">
-        <v>61</v>
-      </c>
-      <c r="C32" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="2">
-        <v>72</v>
-      </c>
-      <c r="C33" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="2">
-        <v>74</v>
-      </c>
-      <c r="C34" s="2">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="2">
-        <v>68</v>
-      </c>
-      <c r="C35" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="2">
-        <v>72</v>
-      </c>
-      <c r="C36" s="2">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="2">
-        <v>72</v>
-      </c>
-      <c r="C37" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" s="2">
-        <v>66</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="C38">
         <v>154</v>
       </c>
     </row>
@@ -2959,16 +4145,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>22</v>
@@ -2980,13 +4166,13 @@
         <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="K1" t="s">
         <v>25</v>
@@ -2995,20 +4181,19 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="2">
+        <v>27</v>
+      </c>
+      <c r="C2">
         <v>74</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>239</v>
       </c>
-      <c r="E2" s="2"/>
       <c r="K2">
         <f>SLOPE(D2:D27,C2:C27)</f>
         <v>5.4125045350102789</v>
@@ -3018,556 +4203,515 @@
         <v>-191.34502358205341</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3">
         <v>63</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>147</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>70</v>
+      </c>
+      <c r="D4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="2">
-        <v>70</v>
-      </c>
-      <c r="D4" s="2">
-        <v>169</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5">
+        <v>68</v>
+      </c>
+      <c r="D5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>72</v>
+      </c>
+      <c r="D6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>73</v>
+      </c>
+      <c r="D7">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C8">
+        <v>71</v>
+      </c>
+      <c r="D8">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>67</v>
+      </c>
+      <c r="D10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>74</v>
+      </c>
+      <c r="D11">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>67</v>
+      </c>
+      <c r="D12">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13">
+        <v>66</v>
+      </c>
+      <c r="D13">
+        <v>209</v>
+      </c>
+      <c r="I13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>69</v>
+      </c>
+      <c r="D14">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
         <v>68</v>
       </c>
-      <c r="D5" s="2">
-        <v>159</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="D15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>67</v>
+      </c>
+      <c r="D16">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>73</v>
+      </c>
+      <c r="D17">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>69</v>
+      </c>
+      <c r="D18">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19">
         <v>72</v>
       </c>
-      <c r="D6" s="2">
-        <v>211</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="D19">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>74</v>
+      </c>
+      <c r="D20">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21">
+        <v>71</v>
+      </c>
+      <c r="D21">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <v>64</v>
+      </c>
+      <c r="D22">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>70</v>
+      </c>
+      <c r="D23">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>65</v>
+      </c>
+      <c r="D24">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25">
+        <v>70</v>
+      </c>
+      <c r="D25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26">
+        <v>62</v>
+      </c>
+      <c r="D26">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27">
+        <v>66</v>
+      </c>
+      <c r="D27">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29">
+        <v>68</v>
+      </c>
+      <c r="D29">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30">
+        <v>71</v>
+      </c>
+      <c r="D30">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31">
         <v>73</v>
       </c>
-      <c r="D7" s="2">
-        <v>239</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="D31">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32">
+        <v>61</v>
+      </c>
+      <c r="D32">
+        <v>128</v>
+      </c>
+      <c r="I32" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="2">
-        <v>202</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2">
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33">
+        <v>61</v>
+      </c>
+      <c r="D33">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34">
+        <v>72</v>
+      </c>
+      <c r="D34">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35">
+        <v>74</v>
+      </c>
+      <c r="D35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36">
+        <v>68</v>
+      </c>
+      <c r="D36">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37">
+        <v>72</v>
+      </c>
+      <c r="D37">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="2">
-        <v>136</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="2">
-        <v>67</v>
-      </c>
-      <c r="D10" s="2">
-        <v>194</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="2">
-        <v>74</v>
-      </c>
-      <c r="D11" s="2">
-        <v>208</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="2">
-        <v>67</v>
-      </c>
-      <c r="D12" s="2">
-        <v>196</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="C38">
+        <v>72</v>
+      </c>
+      <c r="D38">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39">
         <v>66</v>
       </c>
-      <c r="D13" s="2">
-        <v>209</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="I13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="2">
-        <v>69</v>
-      </c>
-      <c r="D14" s="2">
-        <v>175</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="2">
-        <v>68</v>
-      </c>
-      <c r="D15" s="2">
-        <v>177</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="2">
-        <v>67</v>
-      </c>
-      <c r="D16" s="2">
-        <v>186</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="2">
-        <v>73</v>
-      </c>
-      <c r="D17" s="2">
-        <v>205</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="2">
-        <v>69</v>
-      </c>
-      <c r="D18" s="2">
-        <v>210</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="2">
-        <v>72</v>
-      </c>
-      <c r="D19" s="2">
-        <v>193</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="2">
-        <v>74</v>
-      </c>
-      <c r="D20" s="2">
-        <v>186</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="2">
-        <v>71</v>
-      </c>
-      <c r="D21" s="2">
-        <v>138</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="2">
-        <v>64</v>
-      </c>
-      <c r="D22" s="2">
-        <v>163</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="2">
-        <v>70</v>
-      </c>
-      <c r="D23" s="2">
-        <v>185</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2">
-        <v>65</v>
-      </c>
-      <c r="D24" s="2">
-        <v>160</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="2">
-        <v>70</v>
-      </c>
-      <c r="D25" s="2">
-        <v>149</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="2">
-        <v>62</v>
-      </c>
-      <c r="D26" s="2">
-        <v>143</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="2">
-        <v>66</v>
-      </c>
-      <c r="D27" s="2">
-        <v>129</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="2">
-        <v>68</v>
-      </c>
-      <c r="D29" s="2">
-        <v>170</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="2">
-        <v>71</v>
-      </c>
-      <c r="D30" s="2">
-        <v>202</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="2">
-        <v>73</v>
-      </c>
-      <c r="D31" s="2">
-        <v>206</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="2">
-        <v>61</v>
-      </c>
-      <c r="D32" s="2">
-        <v>128</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="I32" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="2">
-        <v>61</v>
-      </c>
-      <c r="D33" s="2">
-        <v>149</v>
-      </c>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="2">
-        <v>72</v>
-      </c>
-      <c r="D34" s="2">
-        <v>235</v>
-      </c>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="2">
-        <v>74</v>
-      </c>
-      <c r="D35" s="2">
-        <v>231</v>
-      </c>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>125</v>
-      </c>
-      <c r="B36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="2">
-        <v>68</v>
-      </c>
-      <c r="D36" s="2">
-        <v>182</v>
-      </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>125</v>
-      </c>
-      <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="2">
-        <v>72</v>
-      </c>
-      <c r="D37" s="2">
-        <v>227</v>
-      </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>125</v>
-      </c>
-      <c r="B38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" s="2">
-        <v>72</v>
-      </c>
-      <c r="D38" s="2">
-        <v>182</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="2">
-        <v>66</v>
-      </c>
-      <c r="D39" s="2">
+      <c r="D39">
         <v>154</v>
       </c>
-      <c r="E39" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3578,16 +4722,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1296344E-A2DF-470F-8386-238FC2790323}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>22</v>
@@ -3599,13 +4743,13 @@
         <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="K1" t="s">
         <v>25</v>
@@ -3614,20 +4758,19 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="2">
+        <v>27</v>
+      </c>
+      <c r="C2">
         <v>74</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>239</v>
       </c>
-      <c r="E2" s="2"/>
       <c r="F2">
         <f>$L$2+$K$2*C2</f>
         <v>209.1803120087072</v>
@@ -3649,20 +4792,19 @@
         <v>-191.34502358205341</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3">
         <v>63</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>147</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3">
         <f t="shared" ref="F3:F27" si="0">$L$2+$K$2*C3</f>
         <v>149.64276212359417</v>
@@ -3676,20 +4818,19 @@
         <v>2.6427621235941672</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="2">
-        <v>70</v>
-      </c>
-      <c r="D4" s="2">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>70</v>
+      </c>
+      <c r="D4">
         <v>169</v>
       </c>
-      <c r="E4" s="2"/>
       <c r="F4">
         <f t="shared" si="0"/>
         <v>187.53029386866612</v>
@@ -3703,20 +4844,19 @@
         <v>18.530293868666121</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="C5">
         <v>68</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>159</v>
       </c>
-      <c r="E5" s="2"/>
       <c r="F5">
         <f t="shared" si="0"/>
         <v>176.70528479864558</v>
@@ -3730,20 +4870,19 @@
         <v>17.705284798645579</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="2">
+        <v>33</v>
+      </c>
+      <c r="C6">
         <v>72</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>211</v>
       </c>
-      <c r="E6" s="2"/>
       <c r="F6">
         <f t="shared" si="0"/>
         <v>198.35530293868666</v>
@@ -3757,20 +4896,19 @@
         <v>12.644697061313337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7">
         <v>73</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>239</v>
       </c>
-      <c r="E7" s="2"/>
       <c r="F7">
         <f t="shared" si="0"/>
         <v>203.76780747369693</v>
@@ -3784,20 +4922,19 @@
         <v>35.232192526303066</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="2">
+        <v>35</v>
+      </c>
+      <c r="C8">
         <v>71</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>202</v>
       </c>
-      <c r="E8" s="2"/>
       <c r="F8">
         <f t="shared" si="0"/>
         <v>192.94279840367639</v>
@@ -3811,20 +4948,19 @@
         <v>9.0572015963236083</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2">
+        <v>36</v>
+      </c>
+      <c r="C9">
         <v>64</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>136</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="F9">
         <f t="shared" si="0"/>
         <v>155.05526665860444</v>
@@ -3838,20 +4974,19 @@
         <v>19.055266658604438</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="2">
+        <v>37</v>
+      </c>
+      <c r="C10">
         <v>67</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>194</v>
       </c>
-      <c r="E10" s="2"/>
       <c r="F10">
         <f t="shared" si="0"/>
         <v>171.29278026363525</v>
@@ -3865,20 +5000,19 @@
         <v>22.707219736364749</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="2">
+        <v>38</v>
+      </c>
+      <c r="C11">
         <v>74</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>208</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="F11">
         <f t="shared" si="0"/>
         <v>209.1803120087072</v>
@@ -3892,20 +5026,19 @@
         <v>1.1803120087072045</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="2">
+        <v>39</v>
+      </c>
+      <c r="C12">
         <v>67</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>196</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="F12">
         <f t="shared" si="0"/>
         <v>171.29278026363525</v>
@@ -3919,20 +5052,19 @@
         <v>24.707219736364749</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="2">
+        <v>40</v>
+      </c>
+      <c r="C13">
         <v>66</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>209</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="F13">
         <f t="shared" si="0"/>
         <v>165.88027572862498</v>
@@ -3946,23 +5078,22 @@
         <v>43.11972427137502</v>
       </c>
       <c r="I13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="2">
+        <v>41</v>
+      </c>
+      <c r="C14">
         <v>69</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>175</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="F14">
         <f t="shared" si="0"/>
         <v>182.11778933365585</v>
@@ -3980,20 +5111,19 @@
         <v>17.642231876238416</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="2">
+        <v>42</v>
+      </c>
+      <c r="C15">
         <v>68</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15">
         <v>177</v>
       </c>
-      <c r="E15" s="2"/>
       <c r="F15">
         <f t="shared" si="0"/>
         <v>176.70528479864558</v>
@@ -4007,20 +5137,19 @@
         <v>0.2947152013544212</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="2">
+        <v>43</v>
+      </c>
+      <c r="C16">
         <v>67</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16">
         <v>186</v>
       </c>
-      <c r="E16" s="2"/>
       <c r="F16">
         <f t="shared" si="0"/>
         <v>171.29278026363525</v>
@@ -4034,20 +5163,19 @@
         <v>14.707219736364749</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="2">
+        <v>44</v>
+      </c>
+      <c r="C17">
         <v>73</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>205</v>
       </c>
-      <c r="E17" s="2"/>
       <c r="F17">
         <f t="shared" si="0"/>
         <v>203.76780747369693</v>
@@ -4061,20 +5189,19 @@
         <v>1.2321925263030664</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="2">
+        <v>45</v>
+      </c>
+      <c r="C18">
         <v>69</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18">
         <v>210</v>
       </c>
-      <c r="E18" s="2"/>
       <c r="F18">
         <f t="shared" si="0"/>
         <v>182.11778933365585</v>
@@ -4088,20 +5215,19 @@
         <v>27.88221066634415</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="2">
+        <v>46</v>
+      </c>
+      <c r="C19">
         <v>72</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19">
         <v>193</v>
       </c>
-      <c r="E19" s="2"/>
       <c r="F19">
         <f t="shared" si="0"/>
         <v>198.35530293868666</v>
@@ -4115,20 +5241,19 @@
         <v>5.3553029386866626</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="2">
+        <v>47</v>
+      </c>
+      <c r="C20">
         <v>74</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20">
         <v>186</v>
       </c>
-      <c r="E20" s="2"/>
       <c r="F20">
         <f t="shared" si="0"/>
         <v>209.1803120087072</v>
@@ -4142,20 +5267,19 @@
         <v>23.180312008707205</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21">
         <v>71</v>
       </c>
-      <c r="C21" s="2">
-        <v>71</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="D21">
         <v>138</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="F21">
         <f t="shared" si="0"/>
         <v>192.94279840367639</v>
@@ -4169,20 +5293,19 @@
         <v>54.942798403676392</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="2">
+        <v>49</v>
+      </c>
+      <c r="C22">
         <v>64</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22">
         <v>163</v>
       </c>
-      <c r="E22" s="2"/>
       <c r="F22">
         <f t="shared" si="0"/>
         <v>155.05526665860444</v>
@@ -4196,20 +5319,19 @@
         <v>7.9447333413955619</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="2">
-        <v>70</v>
-      </c>
-      <c r="D23" s="2">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>70</v>
+      </c>
+      <c r="D23">
         <v>185</v>
       </c>
-      <c r="E23" s="2"/>
       <c r="F23">
         <f t="shared" si="0"/>
         <v>187.53029386866612</v>
@@ -4223,20 +5345,19 @@
         <v>2.5302938686661207</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2">
+        <v>51</v>
+      </c>
+      <c r="C24">
         <v>65</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24">
         <v>160</v>
       </c>
-      <c r="E24" s="2"/>
       <c r="F24">
         <f t="shared" si="0"/>
         <v>160.46777119361471</v>
@@ -4250,20 +5371,19 @@
         <v>0.46777119361470909</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="2">
-        <v>70</v>
-      </c>
-      <c r="D25" s="2">
+        <v>52</v>
+      </c>
+      <c r="C25">
+        <v>70</v>
+      </c>
+      <c r="D25">
         <v>149</v>
       </c>
-      <c r="E25" s="2"/>
       <c r="F25">
         <f t="shared" si="0"/>
         <v>187.53029386866612</v>
@@ -4277,20 +5397,19 @@
         <v>38.530293868666121</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="2">
+        <v>53</v>
+      </c>
+      <c r="C26">
         <v>62</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26">
         <v>143</v>
       </c>
-      <c r="E26" s="2"/>
       <c r="F26">
         <f t="shared" si="0"/>
         <v>144.2302575885839</v>
@@ -4304,20 +5423,19 @@
         <v>1.2302575885838962</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="2">
+        <v>54</v>
+      </c>
+      <c r="C27">
         <v>66</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27">
         <v>129</v>
       </c>
-      <c r="E27" s="2"/>
       <c r="F27">
         <f t="shared" si="0"/>
         <v>165.88027572862498</v>
@@ -4331,25 +5449,19 @@
         <v>36.88027572862498</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="2">
+        <v>55</v>
+      </c>
+      <c r="C29">
         <v>68</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29">
         <v>170</v>
       </c>
-      <c r="E29" s="2"/>
       <c r="F29">
         <f t="shared" ref="F29:F40" si="3">$L$2+$K$2*C29</f>
         <v>176.70528479864558</v>
@@ -4363,20 +5475,19 @@
         <v>6.7052847986455788</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="2">
+        <v>56</v>
+      </c>
+      <c r="C30">
         <v>71</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30">
         <v>202</v>
       </c>
-      <c r="E30" s="2"/>
       <c r="F30">
         <f t="shared" si="3"/>
         <v>192.94279840367639</v>
@@ -4390,20 +5501,19 @@
         <v>9.0572015963236083</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="2">
+        <v>57</v>
+      </c>
+      <c r="C31">
         <v>73</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31">
         <v>206</v>
       </c>
-      <c r="E31" s="2"/>
       <c r="F31">
         <f t="shared" si="3"/>
         <v>203.76780747369693</v>
@@ -4417,20 +5527,19 @@
         <v>2.2321925263030664</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="2">
+        <v>58</v>
+      </c>
+      <c r="C32">
         <v>61</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32">
         <v>128</v>
       </c>
-      <c r="E32" s="2"/>
       <c r="F32">
         <f t="shared" si="3"/>
         <v>138.81775305357363</v>
@@ -4444,23 +5553,22 @@
         <v>10.817753053573625</v>
       </c>
       <c r="I32" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="2">
+        <v>59</v>
+      </c>
+      <c r="C33">
         <v>61</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33">
         <v>149</v>
       </c>
-      <c r="E33" s="2"/>
       <c r="F33">
         <f t="shared" si="3"/>
         <v>138.81775305357363</v>
@@ -4478,20 +5586,19 @@
         <v>14.512186809441618</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="2">
+        <v>60</v>
+      </c>
+      <c r="C34">
         <v>72</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34">
         <v>235</v>
       </c>
-      <c r="E34" s="2"/>
       <c r="F34">
         <f t="shared" si="3"/>
         <v>198.35530293868666</v>
@@ -4505,20 +5612,19 @@
         <v>36.644697061313337</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="2">
+        <v>61</v>
+      </c>
+      <c r="C35">
         <v>74</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35">
         <v>231</v>
       </c>
-      <c r="E35" s="2"/>
       <c r="F35">
         <f t="shared" si="3"/>
         <v>209.1803120087072</v>
@@ -4532,20 +5638,19 @@
         <v>21.819687991292795</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="2">
+        <v>62</v>
+      </c>
+      <c r="C36">
         <v>68</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36">
         <v>182</v>
       </c>
-      <c r="E36" s="2"/>
       <c r="F36">
         <f t="shared" si="3"/>
         <v>176.70528479864558</v>
@@ -4559,20 +5664,19 @@
         <v>5.2947152013544212</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="2">
+        <v>63</v>
+      </c>
+      <c r="C37">
         <v>72</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37">
         <v>227</v>
       </c>
-      <c r="E37" s="2"/>
       <c r="F37">
         <f t="shared" si="3"/>
         <v>198.35530293868666</v>
@@ -4586,20 +5690,19 @@
         <v>28.644697061313337</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" s="2">
+        <v>64</v>
+      </c>
+      <c r="C38">
         <v>72</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38">
         <v>182</v>
       </c>
-      <c r="E38" s="2"/>
       <c r="F38">
         <f t="shared" si="3"/>
         <v>198.35530293868666</v>
@@ -4613,20 +5716,19 @@
         <v>16.355302938686663</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="2">
+        <v>65</v>
+      </c>
+      <c r="C39">
         <v>66</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39">
         <v>154</v>
       </c>
-      <c r="E39" s="2"/>
       <c r="F39">
         <f t="shared" si="3"/>
         <v>165.88027572862498</v>
@@ -4649,9 +5751,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -4659,420 +5765,420 @@
         <v>23</v>
       </c>
       <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s">
         <v>112</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>122</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s">
         <v>95</v>
       </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>109</v>
-      </c>
-      <c r="B37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>110</v>
-      </c>
-      <c r="B38" t="s">
-        <v>60</v>
-      </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
